--- a/05_statistics/paper_level_pathway_summary.xlsx
+++ b/05_statistics/paper_level_pathway_summary.xlsx
@@ -565,11 +565,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>operando/spectroscopy</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
@@ -625,48 +621,44 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>P1;P5</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>P1;P5</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;operando/spectroscopy;operando/spectroscopy;product inference;unknown</t>
+          <t>DFT;product inference</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Operando XAS and XPS results revealed a potentialdataweremeasuredwithfluorescencemodeusingtheAr-filledLytledetector. dependent structure transformation from CuO cluster to Cu –CuN moiety,whichisareversibleprocess.OnceCu –CuN n 3 2 3 clusters have been formed at −1.1V, CO conversion to ethanol OperandoSR-FTIRMeasurements.OperandoSR-FTIRmeasurementswere 2 occurswiththemaximumFE,indicatingtheCu -CuN clusteris conductedattheinfraredspectroscopyandmicrospectroscopystation(BL01B)of 2 3 NationalSynchrotronRadiationLaboratory(NSRL)58.TheCHI660Eelectrothe optimal site. || The Cu L3M45M45 Auger electron spectroscopy 0.14 thefaradaic efficiency(FE)ofasymmetricethanol byconsuming (AES) showed no distinct peak around 918.5eV which indicated electronsandprotons,thehydrogenevolutionreaction(HER),C thatnoCu0 existed onthesurface.TheN K-edgepresentedfour 1 product formation (e.g., CH , HCOOH) and other symmetrical obvious resonances (Fig. 1i) assigned peak A , A , and A to 4 1 2 3 C product formation (e.g., ethylene).</t>
+          <t>Theoretical investigabondformationtoCH CH OH.Similarreactionprocessesbased 3 2 tions were conducted based on DFT calculations to further on *OCHO mechanism were considered for Cu –CuN , as well 3 3 understand the reaction mechanism of the Cu –CuN cluster asCuN andCu–CuN whichcontainedonlyoneactiveCusite, 2 3 3 3 withCH * adsorbed.AsupportedCu –CuN clustermodelwith as shownin Supplementary Fig. 29.Thecalculated overpotential 3 2 3 aCubondingwiththreeNatomsonN-dopedcarbonnanosheets (−0.501V) for Cu –CuN cluster was much lower than that of 2 3 was proposed to be the structure of active sites with an applied CuN (−1.685V), Cu–CuN (−1.368V) and Cu –CuN 3 3 3 3 potential of −1.1V vs. || To further analysis why RDS changed during 3 OCHO (State 9), and then the other *OCHO was reduced to the reaction, the different charge density for Cu -CuN (with/ 2 3 construct*CH +*OCH (State12),thatwentthroughtheC–C without CH * ) and Cu -CuN (with/without CH * ) was 3 2 3 3 3 3 Fig.5DFTcalculationsofCO RRactivity.aReactionprogressofCO toCH CH OHontheCu –CuN at0Vand−0.501Vappliedpotential.The* 2 2 3 2 2 3 showedthereactionsite.Thestatewiththehighestenergybarrier(0.501eV)is8→9.Allstatesinvolvingthetransferofthe(H++e−)pairwere electrochemicalreactionstates,exceptforthe12→13state(CH *+OCH *→OCH CH *),whichwastheC–Cbondformationandnotinfluencedby 3 2 2 3 appliedpotential.bLocalstructuresoftheactivesiteandintermediatestate.Theballsinbrown,blue,red,grayandwhiterepresentCu,N,O,C,andH atoms,respectively. 8 NATURECOMMUNICATIONS| (2022) 13:1322 |https://doi.org/10.1038/s41467-022-29035-8|www.nature.com/naturecommunications || CO molecules interact with two exposed Cu atoms, result suggested the rate-determining steps (RDS) altered when 2 respectively, forming coadsorbed (*OCHO+*OCHO) (State 3). thepotentialatdecreasedto−1.2Vvs.RHE,combiningtheFTIR One adsorbed *OCHO was firstly reduced to form *CH +* results in Fig. 4d.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>main=P1;P5; rejected=P5</t>
+          <t>main=P5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -712,26 +704,34 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;operando/spectroscopy;review;unknown</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>DFT;operando/spectroscopy</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Therefore, the peaks, indexed to the absorbed * OCCOH and * OC H on these atop 2 5 C–C coupling on dCu O/Ag could be triggered under catalysts, exhibit a ratio value for * OC H / * OCCOH on dCu O/ asymmetry between * CO 2 and 2 * . || ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-022-31427-9 Fig.5InsituATR–IRASmeasurementandmechanismfordCu O/Ag .InsituATR–IRASobtainedduringchronopotentiometryinapotentialwindow 2 2.3% 0.2to−1.2V foradCu O,andbdCu O/Ag underCO RR.(Areferencespectrumobtainedat0.3V in1MKOHissubtracted).Potential RHE 2 2 2.3% 2 RHE dependenceofratioofc*CO /*CO andd*OC H /*OCCOHobtainedfordCu O,dCu O/Ag anddCu O/Au .eSchematicforboostedEtOH bridge atop 2 5 2 2 2.3% 2 2.3% generationoverdCu O/Ag .Yellow-color,gray,white,orange,red,andazurespheresinthemodelrepresentH,C,O,Cu1+,Cu0,andAgatoms, 2 2.3% respectively. dCu O/Ag (Fig.5d)42,43.Thisisattributedtotheasymmetric proposed (Fig. 5e).</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>mentioned_only=P5</t>
+          <t>main=P1</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -787,48 +787,44 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P2;P5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
           <t>P2;P5</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P2;P5</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;isotope;product inference;unknown</t>
+          <t>DFT;isotope;product inference;review</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Unfortunately, the formation of C-C bonds on Cu is very complicated and the pathway remains elusive 16, which have greatly limited the development of highly selective electrocatalyst to reduce CO to C (n ≥ 2) liquid products. 2 n Herein, we report a Sn-based tandem catalyst consisting of SnS nanosheets that are able to produce 2 formate intermediates and single Sn atoms anchored on a 3D carbon support via a local SnO3 cluster (Sn -O3G) that generate *OCO(OH) bicarbonate intermediates, followed by C-C coupling to 1 electrochemically reduce CO to ethanol. || These properties can be attributed to the dual active centers of Sn and O in Sn -O3G, 1 which are able to adsorb *CHO and *CO(OH) intermediates, respectively, thereby promoting the subsequent C-C coupling of these intermediates to form ethanol. || From these ndings, we propose that the formation of ethanol over the SnS /Sn -O3G may result from C-C coupling 2 1 between the two intermediates associated with formate and CO. || To date, Cu is the only electrocatalyst found able to 2 generate C (n ≥ 2) liquid products from the CO RR with appreciable reaction rates, due to the strong n 2 adsorption of the *CO intermediate on the Cu surface that promotes C-C bond formation via CO dimerization or CO-CHO coupling 5,12,15. || To verify our hypothesis, we intentionally introduced a small amount of HCOOH into the reaction system (in a Na SO electrolyte instead of KHCO ) during the CO RR over the Sn -O3G.</t>
+          <t>Unfortunately, the formation of C-C bonds on Cu is very complicated and the pathway remains elusive 16, which have greatly limited the development of highly selective electrocatalyst to reduce CO to C (n ≥ 2) liquid products. 2 n Herein, we report a Sn-based tandem catalyst consisting of SnS nanosheets that are able to produce 2 formate intermediates and single Sn atoms anchored on a 3D carbon support via a local SnO3 cluster (Sn -O3G) that generate *OCO(OH) bicarbonate intermediates, followed by C-C coupling to 1 electrochemically reduce CO to ethanol. || These properties can be attributed to the dual active centers of Sn and O in Sn -O3G, 1 which are able to adsorb *CHO and *CO(OH) intermediates, respectively, thereby promoting the subsequent C-C coupling of these intermediates to form ethanol. || atom of Sn -O3 and the C of the support, the Sn -O3G catalyst is distinguished by the dual active sites of 1 1 Sn and O that are able to adsorb different C-based intermediates, providing a novel platform for C-C bond formation during the CO RR to produce ethanol. 2 In summary, we have developed a Cu-free, Sn-based tandem catalyst to produce ethanol from the CO RR, 2 in which the dual active centers of Sn and O atoms on Sn -O3G serve to adsorb different C-based 1 intermediates, which effectively lowers the C-C coupling energy between *CO(OH) and *CHO. || These results demonstrate the importance of HCOOH in C-C coupling to form ethanol on O atoms coordinated Sn catalytic sites. || Therefore, 3 2 2 Fig. 3f schematically summarizes the CO RR process to form ethanol taking place on the SnS /Sn -O3G. 2 2 1 The comprehensive discussion for the ethanol formation process on the SnS /Sn -O3G tandem catalyst 2 1 is provided from additional structural characterization and kinetics simulation (Extended data Figs. 49– 53 and Tables 9–17), indicating that diffusion of HCOOH generated from the SnS component to the 2 single atomic Sn sites on Sn -O3G is the rate-determining step for ethanol formation. 1 Based on the above experimental results, we built the active site model of the catalyst.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>main=P1;P2;P5</t>
+          <t>main=P2;P5</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -879,7 +875,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>DFT;product inference</t>
+          <t>review</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -946,39 +942,35 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>operando/spectroscopy;operando/spectroscopy;product inference;product inference</t>
+          <t>operando/spectroscopy;review;unknown</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Cu-composedelectrodeinpreviousstudies39–41.However,thecatalyst AccordingtotheSEMimages,XRDprofilesandOH−electroadsorption inthisstudycontributestotheimprovedC product,whichisascri2+ measurement, the morphology and dominant exposed facets of Cu bedtothenewreductionpathwaysofCO RRafterwettabilitymod2 catalyst are not significantly changed (Supplementary Figs. 18–20). ification.Thus,thechemicalstructureormorphologychangingafter XPSanalysisbeforeandaftertheelectrolysisrevealsimilarCu/Sratios thiol-modified is not the reason for improved CO RR selectivity of 2 onthecatalystsurface(SupplementaryFig.21).TheHRTEMdisplays ethyleneandethanol. the presence of the alkanethiol layer on the Cu catalyst after the reactionduetothehighelectrochemicalstabilityofthehydrophobic Effectofcontrollablewettabilityon*COcoverageviaCO mass 2 layer(SupplementaryFig.22).Thehydrophobic-treatedelectrodecan transport maintainalargercontactangleafterelectrolysis,whichascribestothe ItisknownthatthemasstransportofCO (localCO concentration) 2 2 optimized wettabilityofthecatalystlayerthatimprovestheCO RR can affect the coverage of *CO (a precursor of *CO), *CO, and *H, 2 2 stability (Supplementary Fig. 23).</t>
+          <t>*H and *CO occupy most of the Cu coverage)onthesurface.Theseresultssuggestthatthevariationof 2 surfacesites,resultingindirectcompetitionbetween*Hand*COfor the interface contact state derived from the interfacial wettability surfacesites47.Whenthesurfacemaintainsahigh*COcoverage,the affects both CO and H O transport, which may be a solution for 2 2 corresponding *H coverage will decrease12,18,46,47.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>main=P1; rejected=P1</t>
+          <t>main=P1</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1022,45 +1014,21 @@
           <t>ETOH_012_10.1038_s41467-023-36926-x.txt</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>product inference;review</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>The RHE)ofethanolforCO R,whichis0.09Vforethanol39. 2 catholyteofpH1were0.05Msulfuricacid(HSO )and3Mpotassium The C selectivity was calculated as (the rate of C product 2 4 2+ 2+ chloride(KCl)solution,andpHwasadjustedtoaround1byafewdrops formation (R ))/(the rate of total product formation (R )), as product tot of5Mpotassiumhydroxide(KOH).ThecatholyteofpH4were3MKCl follows: solution,andpHwasadjustedtoaround4byafewdropsofH SO . 2 4 ThecatholyteofpH7were3MKClsolution,andpHwasadjustedto C 2+ selectivity=ð2R ethylene +2R acetate +2R ethanol +3R n(cid:3)propanol Þ= around7byafewdropsof1MKOH.ThecatholyteofpH13.5were ðR +R +R +2R +2R ð7Þ CO formate methane ethylene acetate 0.75MKOHsolution.TheanolyteofpH1and4were0.5MH SO ,the anolyte of pH 7 were 1M KHCO , and the anolyte of pH 1 2 3.5 4 were +2R ethanol +3R n(cid:3)propanol Þ×100%, 3 0.75M KOH.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>main=P5; mentioned_only=P1; rejected=P1</t>
-        </is>
-      </c>
+          <t>DFT</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1070,7 +1038,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1109,33 +1077,17 @@
           <t>ETOH_014_10.1021_acscatal.3c00190.txt</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>product inference</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>mentioned_only=P1</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1145,7 +1097,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1186,44 +1138,48 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>P1;P2;P3;P5;P6</t>
+          <t>P1;P3;P6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>P1;P3;P5</t>
+          <t>P1;P3;P6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>P1;P2;P3;P5;P6</t>
+          <t>P1;P3;P6</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>DFT;isotope;DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;isotope;operando/spectroscopy;product inference;product inference;unknown</t>
+          <t>DFT;operando/spectroscopy;product inference;review;unknown</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Consistent with previous reports14,15, the observing analogous signals on a different Cu foil with distinct surface signals appearing at 1,450 cm−1 and 1,550 cm−1 from −0.76 V can be morphology, yet with still good performance towards C products RHE 2+ attributed to *OCCO(H), with the C=O vibration mode (Fig. 3 and Sup- (Supplementary Fig. 19). plementary Tables 4 and 5). || RHE 2 2 the 1,455 cm−1 and 1,602 cm−1 peaks, in addition to the CO stretching Overall, the presence of CO molecules on the Cu surface during CORR 2 (2,100 cm−1), Cu–CO stretching (358 cm−1) and CO rotation (275 cm−1) is linked to and probably causes the formation of *CO–CO or *CO–COH bands, proving that these peaks are related to the CORR process. || Alternatively, such frequencies can be As ethanol and acetaldehyde are the main C products for gly2 assigned to an OCCO− dimer adsorbed on surface oxygen (O), known oxal reduction on polycrystalline copper and are proposed to share s as deprotonated glyoxylate OCOCO2− (ref. 36), which also shows the the same *OCHCH intermediate16–18, we performed in situ Raman s 2 1,070 cm−1 band detected at −0.76 V (Supplementary Table 6). experiments of glyoxal and ethanol reduction (Supplementary Figs. 20 RHE Among other additional possible intermediates (*OCCHO, *OHCand 21). || Two new peaks at ∼1,390 cm−1 and ∼1,610 cm−1 appear, which are a potential switch from −0.36 V RHE to −0.96 V RHE (Supplementary Fig. 14). attributed to the symmetric and asymmetric stretching vibrations Concurrently, a broad band in the range of 2,830–2,990 cm−1 appeared, of carboxyl(ate) groups, respectively, based on control experiments which can be attributed to the stretching band of C–H (ref. 12). in Ar-saturated NaClO with 1 mM HCOOH solution (Supplementary 4 Fig. 13) and in Ar-saturated KHCO solution (Supplementary Fig. 11). || Furthermore, from −0.85 V RHE OD-Cu sites (Supplementary Fig. 24 and Supplementary Table 16). onwards, undercoordinated distorted sites with high surface strain Besides, both crystalline and distorted morphologies with coordinaand deep s-band states originate (Fig. 5c,e) and enable the formation tion number below 8 show strong CO binding (&lt;−0.2 eV). of OCHCH at the surface (Fig. 6b), detected experimentally through 2 Localized compressive strain plays a crucial role in stabilizing Raman spectroscopy (Figs. 2c and 3) together with the production of *OCHCH species on distorted sites (red empty data points in Fig. 6a). ethanol (Fig. 1f). 2 In fact, *OCHCH formation energies increase following the increA careful comparison of ethylene, ethanol and methane Fara2 ment of compressive strain, and stronger binding is observed on daic efficiency versus CO selectivity (taken from Fig. 1f) confirms the undercoordinated distorted sites rather than crystalline sites.</t>
+          <t>C–O stretching bands with intermediate frequencies (2,075 cm−1 and On the basis of these mechanistic insights, we aimed to correlate 2,090 cm−1) become the main contribution at −0.76 V , from which specific active sites and reaction intermediates with ethylene and RHE the *OCCO intermediate is identified and ethylene is produced, in line ethanol production during CORR. || All spectra were aligned by 3 hyde/CO reduction20, we here identify *CHCO reduction to *OCHCH fixing the Cu 2p of Cu0 and Cu+ to 932.67 eV as a reference. 2 3/2 as the selectivity switch (selectivity-determing step 2, SDS2) to ethanol, acetaldehyde, 1-propanol and allyl alcohol (Supplementary In situ Raman experiments Note 1 and Supplementary Figs. 28 and 29), as confirmed by the The in situ Raman spectra were obtained using a Renishaw (InVia strong correlation between acetaldehyde and ethanol selectiviReflex) confocal Raman microscope with a 785 nm laser. || Thus, we In addition, we carried out 13Cor D-labelling SERS experiments reasonably confirmed the detection of a common intermediate along at −0.95 V (Fig. 4a). 13C/12C exchange led to obvious redshifts of the CO, CO and glyoxal reduction route to ethanol, which is *OCHCH. || However, defects characterized by conditions at the surface of the catalyst. 2+ a highly compressed and distorted coordination environment and deep s-band states are instead generated at higher overpotentials and CORR testing 2 stabilize the adsorption of OCHCH via the terminal oxygen, opening Electrocatalytic measurements were performed with a Biologic SP-240 2 an alternative selective route towards ethanol on copper. || The objective with a long working distion intermediate, which is reasonably OCHCH (Supplementary tance was needed to avoid diffusion hindrance during the Raman 2 Fig. 28).</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>main=P1;P3;P5; mentioned_only=P2;P6</t>
+          <t>main=P1;P3;P6; rejected=P6</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1269,48 +1225,44 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>P1;P2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>P1;P2;P5</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown</t>
+          <t>DFT;isotope;operando/spectroscopy;review</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Article https://doi.org/10.1038/s41467-024-54636-w Manipulating C-C coupling pathway in electrochemical CO reduction for selective 2 ethylene and ethanol production over single-atom alloy catalyst Received:28February2024 ShifuWang1,2,9,FuhuaLi3,4,9,JianZhao2,YaqiongZeng2,YifanLi 5,Zih-YiLin6, Tsung-JuLee6,ShuhuiLiu7,XinyiRen2,WeijueWang2,YusenChen2, Accepted:14November2024 Sung-FuHung 6,Ying-RuiLu 8,YiCui 5,XiaofengYang 2,XuningLi 2 , YanqiangHuang 1,2 &amp;BinLiu 3,4 Checkforupdates ManipulationC-CcouplingpathwayisofgreatimportanceforselectiveCO 2 electroreductionbutremainchallenging.Herein,twomodelCu-basedcatalysts,bymodifyingCunanowireswithAgnanoparticles(AgCuNW)andAg singleatoms(AgCuNW),respectively,arerationallydesignedforexploring 1 theC-CcouplingmechanismsinelectrochemicalCO reductionreaction 2 (CO RR).ComparedtoAgCuNW,theAgCuNWexhibitsamorethan10-fold 2 1 increaseofC selectivityinCO reductiontoethanol,withethanol-to-ethylene 2 2 ratioincreasedfrom0.41overAgCuNWto4.26overAgCuNW.Viaavarietyof 1 operando/in-situtechniquesandtheoreticalcalculation,theenhancedethanol selectivityoverAgCuNWisattributedtothepromotedH Odissociationover 1 2 theatomicallydispersedAgsites,whicheffectivelyaccelerated*COhydrogenationtoform*CHOintermediateandfacilitatedasymmetric*CO-*CHO couplingoverpairedCuatomsadjacenttosingleAgatoms.Resultsofthis workprovidedeepinsightintotheC-CcouplingpathwaystowardstargetC 2+ productandshedlightontherationaldesignofefficientCO RRcatalystswith 2 pairedactivesites. || Isotopic labelling experiments microscopy(FESEM,JSM-6700F)equippedwithanenergydispersive 1 indicated that the methyl C (*CH ) and methylene C (*CH OH) in X-rayspectroscopy(EDX,AztecX-Max80T).High-angleannulardark3 2 ethanol product were originated from the *CO and *HCHO interfield scanning transmission electron microscopy (HAADF-STEM) mediates,respectively.Theoreticalcalculationsfurtherdemonstrated characterizationwasconductedonaJEOLJEMARM200FSTEM/TEM thattheatomicallydispersedAgcouldnotonlypromotedissociation withaguaranteedresolutionof0.08nm.DetailedchemicalcomposiofH OtoreleaseH+,butalsoreducetheenergybarrierforthefortionswereanalyzedbyX-rayphotoelectronspectroscopy(XPS)onan 2 mation of *CHO over its neighboring Cu site, resulting in the sigESCALAB250photoelectronspectrometer(ThermoFisherScientific) nificantly promoted asymmetric *CO-*CHO coupling over paired Cu using a monochromatic Al Kα X-ray beam (1,486.6eV). || *OHoverAgCuNWduringCO RR.Todeterminethe*OHadsorption Basedontheaboveresults,thereactionmechanismsofCO RRfor 1 2 2 site,theadsorptionanddissociationenergiesofH OonCuNW,AgCu thedistinctiveselectivitytowardsethyleneandethanoloverAgCuNW 2 NWandAgCuNWwerecalculated17.AsshowninFig.5a,comparedto andAgCuNWcanbeclearlyevidenced.Theethylenepathwayfollows 1 1 AgCuNWandCuNW,theH OadsorptionenergyoverAgCuNWis the symmetric C-C coupling, arising from the high *CO coverage 2 1 more negative with more electrons directly transferred from H O generatedoverAgnanoparticlesandthereducedenergybarrierfor 2 molecule to AgCu NW (Supplementary Fig. 50).</t>
+          <t>Furthermore, H O *COCOformationoverAgCuNW.Whiletheethanolpathwayfollows 1 2 tendstomorepreferablydissociateonthesingleAgatomicsiteover theasymmetricC-Ccoupling,triggeredbythein-situgeneratedHOAgCuNWwiththelowestH Odissociationtransitionstate(TS)energy Ag-Cu-Cu sites (Fig. 5e), which reduces the energy barrier for the 1 2 1 barrier(Fig.5bandSupplementaryFigs.51–53).Thein-situformation formationof*CHOspeciesandthuspromotesasymmetric*CO-*CHO ofHO-AgCuNWduringCO RRnotonlypromotedthereleaseofH+ coupling,boostingCO reductiontoethanoloverAgCuNW. 1 2 2 1 forthesubsequenthydrogenationreaction,butalsolargelyreduced theGibbsfreeenergyfor*COhydrogenationto*CHO(Fig.5c),which Discussion facilitated the asymmetric *CO-*CHO coupling over the adjacent Insummary,twowell-definedmodelCu-basedcatalystsweredevelpairedCuatoms(HO-Ag-Cu-Cu)topreferablyreduceCO toethanol opedbymodifyingCunanowireswithAgnanoparticles(AgCuNW) 1 2 (Fig. 5d, e,and SupplementaryFigs. 54–57).On the other hand, for andsingleAgatoms(AgCuNW),respectively,andtheirunderlying 1 AgCuNW,asshowninSupplementaryFigs.58–60,theenergybarrier C-C coupling mechanisms of CO RR to ethylene and ethanol were 2 forhydrogenationof*CO to*COOHcanbegreatlyreducedfrom0.83 successfullyelucidated.OperandoXASandquasiin-situXPSrevealed 2 NatureCommunications|( 2024)1 5:10247 7 || Article https://doi.org/10.1038/s41467-024-54636-w Manipulating C-C coupling pathway in electrochemical CO reduction for selective 2 ethylene and ethanol production over single-atom alloy catalyst Received:28February2024 ShifuWang1,2,9,FuhuaLi3,4,9,JianZhao2,YaqiongZeng2,YifanLi 5,Zih-YiLin6, Tsung-JuLee6,ShuhuiLiu7,XinyiRen2,WeijueWang2,YusenChen2, Accepted:14November2024 Sung-FuHung 6,Ying-RuiLu 8,YiCui 5,XiaofengYang 2,XuningLi 2 , YanqiangHuang 1,2 &amp;BinLiu 3,4 Checkforupdates ManipulationC-CcouplingpathwayisofgreatimportanceforselectiveCO 2 electroreductionbutremainchallenging.Herein,twomodelCu-basedcatalysts,bymodifyingCunanowireswithAgnanoparticles(AgCuNW)andAg singleatoms(AgCuNW),respectively,arerationallydesignedforexploring 1 theC-CcouplingmechanismsinelectrochemicalCO reductionreaction 2 (CO RR).ComparedtoAgCuNW,theAgCuNWexhibitsamorethan10-fold 2 1 increaseofC selectivityinCO reductiontoethanol,withethanol-to-ethylene 2 2 ratioincreasedfrom0.41overAgCuNWto4.26overAgCuNW.Viaavarietyof 1 operando/in-situtechniquesandtheoreticalcalculation,theenhancedethanol selectivityoverAgCuNWisattributedtothepromotedH Odissociationover 1 2 theatomicallydispersedAgsites,whicheffectivelyaccelerated*COhydrogenationtoform*CHOintermediateandfacilitatedasymmetric*CO-*CHO couplingoverpairedCuatomsadjacenttosingleAgatoms.Resultsofthis workprovidedeepinsightintotheC-CcouplingpathwaystowardstargetC 2+ productandshedlightontherationaldesignofefficientCO RRcatalystswith 2 pairedactivesites. || Isotopic labelling experiments microscopy(FESEM,JSM-6700F)equippedwithanenergydispersive 1 indicated that the methyl C (*CH ) and methylene C (*CH OH) in X-rayspectroscopy(EDX,AztecX-Max80T).High-angleannulardark3 2 ethanol product were originated from the *CO and *HCHO interfield scanning transmission electron microscopy (HAADF-STEM) mediates,respectively.Theoreticalcalculationsfurtherdemonstrated characterizationwasconductedonaJEOLJEMARM200FSTEM/TEM thattheatomicallydispersedAgcouldnotonlypromotedissociation withaguaranteedresolutionof0.08nm.DetailedchemicalcomposiofH OtoreleaseH+,butalsoreducetheenergybarrierforthefortionswereanalyzedbyX-rayphotoelectronspectroscopy(XPS)onan 2 mation of *CHO over its neighboring Cu site, resulting in the sigESCALAB250photoelectronspectrometer(ThermoFisherScientific) nificantly promoted asymmetric *CO-*CHO coupling over paired Cu using a monochromatic Al Kα X-ray beam (1,486.6eV). || *OHoverAgCuNWduringCO RR.Todeterminethe*OHadsorption Basedontheaboveresults,thereactionmechanismsofCO RRfor 1 2 2 site,theadsorptionanddissociationenergiesofH OonCuNW,AgCu thedistinctiveselectivitytowardsethyleneandethanoloverAgCuNW 2 NWandAgCuNWwerecalculated17.AsshowninFig.5a,comparedto andAgCuNWcanbeclearlyevidenced.Theethylenepathwayfollows 1 1 AgCuNWandCuNW,theH OadsorptionenergyoverAgCuNWis the symmetric C-C coupling, arising from the high *CO coverage 2 1 more negative with more electrons directly transferred from H O generatedoverAgnanoparticlesandthereducedenergybarrierfor 2 molecule to AgCu NW (Supplementary Fig. 50). || Additional new peaks at around 1244cm−1 and NW, where methyl C (-CH ) and methylene C (-CH OH) in ethanol 1 3 2 1083cm−1 were observed on AgCu NW, which can be assigned to originatefrom*COand*HCHOintermediates,respectively. 1 adsorbed*CHOand*COCHOintermediates,respectively(Fig.4e)60.As showninFig.4f,thepeakintensityof*COCHOintermediatewasfound Theoreticalinsightsintothecatalyticmechanism tograduallyincreasewithincreasingappliedcathodicpotentialfrom Densityfunctionaltheory(DFT)calculationswereperformedtogain −0.4to−1.2VvsRHE,whilethepeakintensityof*CHOintermediate insightsintotheunderlyingreactionmechanismsforthedistinctive was correspondingly decreased, suggesting production of *COCHO selectivityofCO electroreductiontoethyleneandethanoloverAgCu 2 intermediatefromasymmetric*CO-*CHOcoupling.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>main=P1;P2; mentioned_only=P5</t>
+          <t>main=P2</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1354,18 +1306,38 @@
           <t>ETOH_023_10.1038_s41467-025-67176-8.txt</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>P1;P3;P4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>P1;P3;P4</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>P1;P3;P4</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;unknown</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+          <t>DFT;operando/spectroscopy;product inference;unknown</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Deciphering Ethanol Reaction Pathways EtOH and C H follow similar CO ER pathways, both undergoing protonation to the shared 2 4 2 intermediate *CHCO, where the bonding configuration of its protonated form *CHCHO plays a || The asymmetric coupling of OCCOH was triggered by promoting a mixed adsorption configuration of *CO and *CO . || The complete reaction pathway from CO to EtOH on Co -Sub-CuS is as follows: 2CO 2 0.050 2 → 2*COOH → *CO + *CO → *COH + *CO → *OCCOH → *CCO → *CHCO → bridge atop atop *CHCHO* → *OCHCH → *OCHCH → *OCH CH → C HSOH (Fig. 3k).</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>main=P1;P3;P4</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>no</t>
@@ -1373,12 +1345,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1391,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P1;P2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1427,44 +1399,36 @@
           <t>P1;P2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>P1;P2;P5</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P1;P2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;product inference;product inference</t>
+          <t>operando/spectroscopy</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Specifically, for the system without CA, the 3800cm−1positionoftheRamanspectra,theO–Hstretchingvibration 2 *OCCOH,*OC H intermediatescorrespondingtothesynthesisofC can be decomposed into three types according to Gaussian fitting 2 5 2+ productsandC HOHlocatedat1210and1350cm−1aswellasthe*CHO (SupplementaryFig.17)45,46.Revealedbyexistingfindings43,47,K+inthe 2 5 and*OCH intermediatesassociatedwiththeformationofCH at1480 electrolytewasmorelikelytobespecificallyadsorbedontheelectrode 3 4 and1410cm−1wereclearlydetected40–42.Differently,inthepresenceof surface.</t>
+          <t>Specifically, for the system without CA, the 3800cm−1positionoftheRamanspectra,theO–Hstretchingvibration 2 *OCCOH,*OC H intermediatescorrespondingtothesynthesisofC can be decomposed into three types according to Gaussian fitting 2 5 2+ productsandC HOHlocatedat1210and1350cm−1aswellasthe*CHO (SupplementaryFig.17)45,46.Revealedbyexistingfindings43,47,K+inthe 2 5 and*OCH intermediatesassociatedwiththeformationofCH at1480 electrolytewasmorelikelytobespecificallyadsorbedontheelectrode 3 4 and1410cm−1wereclearlydetected40–42.Differently,inthepresenceof surface. || The K+-coordinated water (denoted as K+ H O) will con2 CA, the *OCCOH and *OC H were extraordinarily stronger in the tinuouslysupplyH Otoelectrodesurfaceaswellasacceleratedthe 2 5 2 intensities and dramatically easier than the formation of *CHO and HERkinetics,whichwasmoresignificantlyyeteffectivelyforHERthan *OCH intermediatesfortheformation ofCH ,distinctlyillustrating theothertwostructuraltypesofH O(2-,4-coordinatedH-bondwater, 3 4 2 that the C HOH and C products werefavorablyformed over the whichweredenotedas2-HBH Oand4-HBH O).Thein-situRaman 2 5 2+ 2 2 developed catalyst.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>main=P1;P2; mentioned_only=P5; rejected=P1;P2;P5</t>
+          <t>main=P1;P2</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1515,7 +1479,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;operando/spectroscopy</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1571,34 +1535,14 @@
           <t>ETOH_B2_003_10.1002_anie.202017070.txt</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>DFT;operando/spectroscopy;operando/spectroscopy;product inference</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>mentioned_only=P2; rejected=P5</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>no</t>
@@ -1606,12 +1550,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1655,11 +1599,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>operando/spectroscopy;product inference</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
@@ -1713,41 +1653,21 @@
           <t>ETOH_B2_005_10.1038_s41467-021-27456-5.txt</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;product inference;operando/spectroscopy;product inference</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>ARTICLE NATURECOMMUNICATIONS|https://doi.org/10.1038/s41467-021-27456-5 firstlyelectrodepositedongasdiffusionlayer(GDL,Sigracet22BB,FuelCellStore) QuantificationoftheCO 2 RRproducts.Theelectrochemicaldatawererecorded usedasgasdiffusionelectrode(GDE)andthenfunctionalsolutionsweredropwhilesimultaneouslycollectingtheCORRgasproductsbyusinganautomatic 2 coatedonthecatalystside,whiletheothersideoftheGDLwascoveredwith samplerconnectedtothecathodeoutlet.Acoldtrapwasusedtocollecttheliquid polyamidetape.TheGDLwasthentapeonagraphitefoilandsubsequently,the productsbeforethesampler.Foreachappliedpotential,thegasproductswere electrodewasmountedinanoperandocellwiththegraphitefoilactingasa collectedatleastthreetimeswithpropertimeintervals.Thegasaliquotswerethen workingelectrodeandwindow.A0.5MsolutionofKHCO wasusedaselectrolyte injectedintoanonlinegaschromatograph(Agilent,MicroGC-490)equippedwith 3 fortheCORRandthecellwascontinuouslypurgedwithCO duringthemeaaTCDdetectorandMolsieve5Acolumncontinuously.Hydrogenandargon 2 2 surements.Allmeasurementswereperformedatconstantpotentialsof−1.2V, (99.9999%)wereusedasthecarriergases.Liquidproductswerequantifiedby1H −1.1V,−1.0Vand−0.9Vvs.RHE.Time-resolvedspectrawererecordedevery NMRspectroscopy(600MhzAvanceIIIBukrerwithacryorobeProdigyTCI) 30minuntilnofurtherchangeswereobservedunderCORRconditions. usingdeionizedwaterwith0.1%(w/w)ofDSS(Sodiumtrimethylsilylpropane2 DataalignmentandnormalizationoftheX-rayabsorptionnear-edgestructure sulfonate)likeinternalstandardforthequantificationoftheethanolandformate.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>main=P5</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1757,7 +1677,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1796,24 +1716,32 @@
           <t>ETOH_B2_006_10.1038_s41467-020-20615-0.txt</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;operando/spectroscopy;product inference;unknown</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>DFT;review</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Two disparate scaling relationship can be likegrainboundariesandvacanciesexist(SupplementaryFig.13). obtained between the average adsorption energy of two binding Up to now, authentic OD-Cu surface structures are obtained *CO (E(CO)) and coupled intermediate *COCO (E(COCO)) on based on NN-MD simulation of the whole reduction process. the non-square sites and square sites.</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>rejected=P1</t>
+          <t>main=P1</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1823,12 +1751,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1872,11 +1800,7 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>operando/spectroscopy</t>
-        </is>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
@@ -1930,18 +1854,30 @@
           <t>ETOH_B2_009_10.1021_acs.accounts.1c00650.txt</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>DFT;product inference</t>
+          <t>product inference</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>mentioned_only=P5</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>no</t>
@@ -1949,12 +1885,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1998,11 +1934,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>operando/spectroscopy</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
@@ -2058,52 +1990,48 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>P1;P4;P5</t>
+          <t>P1;P5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>P1;P5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>P1;P4;P5</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>P1;P4;P5</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;product inference;unknown</t>
+          <t>DFT;operando/spectroscopy;product inference;review;unknown</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>When applying a bias of –1.3V, the formation of structure (R-Hex-2Cu-O/G), which was used for all reaction *HOCCOHbecomesthermodynamicallydownhill(ΔE=–0.87eV)with mechanismstudy. aloweractivationenergybarrierof0.72eV,leadingtoanacceptable WefirstscrutinizedthekeyreactionintermediatesforC–Ccoureactionrateatroomtemperature46.Ourcalculationalsoconfirms*CO plingonR-Hex-2Cu-O/G,includingtwoCu-adsorbed*CObeforecoutrimerization to form n-propanol is facilitated by the spatialplingandthe*OCCOHdirectlyaftercoupling.Formostoftheactive confinementeffectonR-Hex-2Cu-O/G(SupplementaryFig.36b).The sitesexplored,alinearrelationshipexistsbetweenthetwoadsorption C pathwaytowardn-propanolisshowninFig.5candSupplementary 3 strengths(i.e.,ΔG andΔG )asshowninFig.5aandSuppleFig.40;theU is–0.98V,similartothatforethanolproduction, 2*CO *OCCOH limiting mentary Fig. 35. || (Cu )immobilizedontheCu-reduction-inducedvacancyonHex-2CuOurexperimentsobserveaselectivityincreaseforethylenepro9 O,anddenotedasR-Hex-2Cu-O.ThecurvedstructureofHex-2Cu-O duction starting from –1.3V on Hex-2Cu-O (Supplementary Fig. 7), formsaconfinedspacebetweentheCu clusterandtheadjacentsingle whichisrationalizedbycalculationssuggestingthattheaccelerated 9 Cucenter,whichare~3.84Åapart(SupplementaryFig.34).Thismodel reactionkinetics is led by the decreased activationbarrier with the isreasonableconsideringthesimilarsizeoftheCuclustertothatofthe changeofelectrodepotential.Figure5eshowsthatat0VvsRHEthe hexaphyrinmolecule(Fig.3d).Furthermore,toincludetheimpactof formation of *HOCCOH is kinetically unfavored on R-Hex-2Cu-O/G carbon-basedconductingagentKetjenBlack(KB)intheexperiment,a with an activation energy barrier of 1.51eV (MEP shown in Supple5×5×1 graphene substrate was introduced to support the hybrid mentary Fig. 39). || Elemental analysis further shows that the Cu clusters CuclustersduringCO RRwasalsowitnessedbyTime-lapseXAFSata remainedontheelectrodeaccountfor∼82%oftheoriginalCucon2 constantpotentialof−1.2V(SupplementaryFig.25).Injust8min,Cu tent, and that the N content isnotably reduced after soaking (Supcentersinthecomplexwerealreadypartiallyreduced,aswitnessedby plementaryTable5).InthesubsequentretestingofCO RR,theFEof 2 thecoexistenceofCu0andCu–N/OspeciesinboththeXANESandFTmulti-carbonproductsat−1.2Vdecreasesfrom66.2%fortheoriginal EXAFSspectra.After24min,thewholecatalystsystemwasstabilized, catalystto22.1%,inwhichethanolandn-propanolaccountforonly withsimilarCuoxidationandcoordinationstatestilltheendofthe 8.8%and8.2%,respectively.Meanwhile,thetotalefficiencyofC pro1 test.ItisthussurmisedthatmetallicCureducedfromorganometallic ducts(includingformate,COandmethanol)increasesfrom16.3%to precursorsmightimposeself-constraintonparticlegrowthduetothe 40.3%(SupplementaryFig.32).Thisresultissomehowsimilartothe ligand tethering effect and catalyst-support interaction, which have productdistributionobservedonOct-2Cu,whichformscopperclusbeen demonstrated in previous literature reports4,33,34, and further ters and fragmented ligands during electrolysis. || For Hex-2Cu-O, each of the two copper mainlyCOandformateatlowoverpotentials(Fig.2a).Startingfrom ions is bound to one bridging meso-oxygen atom and three pyr- −1.1V and beyond, C products including ethylene, ethanol and n2+ rolic nitrogen atoms in a distorted quadrilateral configuration. propanolconstitutethemainCO RRproducts.Inparticular,at−1.2V 2 The central Cu–O–Cu bonding fights against the tension of the thetotalFaradaicefficiency(FE)ofmulti-carbonalcoholsincreasesto expandedporphyrin,resultinginagabledstructurewithaCu–Cu 50.8%(ethanol:32.5%;n-propanol:18.3%),whichhasbeenrarelyseen distanceof3.7Å(Fig.1a).InHex-2Cu-2O,thedoublyN-confused intheliterature(SupplementaryTable2).At−1.3V,thetotalFEofC 2+ hexaphyrinprovidestwocarbonyloxygenstoallowbothcopper products reaches to its maximum of 71% (Supplementary Fig. 6). ions to be independently anchored by the surrounding three N Afterwards,boththeFEsofethanolandn-propanoldecreases,whereas and one O atoms, also in a square-planar geometry but with theFEandpartialcurrentdensityofethylene continuallyrise (Supmilder Cu-O strain. || However, some reaction sites significantly deviate and therefore agrees well with the experimental observation for a fromthislinearrelationship,withΔG decreasesfromthetrendnotableselectivitytowardn-propanol(Fig.2a).Nonetheless,itisworth *OCCOH fittedlevelsof1.27,1.21eVto0.92,0.90eV,respectively.ThesereactonotethatgiventhecomplexphasespacedemonstratedbyR-Hextionsitesarethosewithintheconfined-spacebetweentheCu cluster 2Cu-2O/Gthatwouldrequireas-of-yetunrealizedsimulationcapability 9 and the adjacent single Cu center (Supplementary Fig. 35), with an toconclusivelydepict,themechanismproposedhereispendingfor extrabondformedbetweentheadsorbed*OCCOHandadjacentCu furtherclarificationtounderstandthecausalfactorsfromelectronic center (Supplementary Fig. 36a).</t>
+          <t>We adopted the selectivity determining method linearscalingrelationwith*CO.Next,CO RRproceedspreferentially 2 proposedbyRossmeisletal45todecidetheproductselectivityonRtowardC HOHformationthroughtheexergonicprotonationonCto 2 5 Hex-2Cu-O/G.TheresultsinFig.5bshowthatallactivesitesfromtheRfrom*OCHCOH,whereastheprotonationonOtoform*HOCCOHis Hex-2Cu-O/G surface (Supplementary Fig. 37) fell in the CO RR disfavoredowingtotheextraenergyneededtocleavetheO–Cubond. 2 dominantzone.Thecalculatedselectivityonthetwomodelsisingood Lastly,theelectrochemicalCO RRofHex-2Cu-Owasfurthertestedina 2 agreementwiththeexperimentalobservationofstableC andalcohol flow-cell using the aqueous 1M KOH electrolyte. || Fig.38).TheprotonationonCtoform*OCHCOH,followedbysubAlltheconstructedmodelsarelistedinSupplementaryFig.34. sequenthydrogenation,canbewellsupportedbythereactioninterAftergeometryoptimization,thestructureofHex-2Cu-Obendstoa mediatesdetectedbyATR-SEIRAS,especiallythestretchingoftheC–C curvedshape,coincidingwiththemolecularstructuredeterminedby coupling intermediate—*OCCOH and the C HOH precursor— 2 5 X-raycrystallography23,24.ThehybridstructureofCuclusterandpar- *OCH CH around1436and1360cm−1,respectively(Fig.4c),whichin 2 3 tially reduced Hex-2Cu-O is represented by a nine Cu atom cluster turnqualitativelyvalidatestheproposedethanolpathway(Fig.5d). || The reaction pathways are 2 5 2 4 3 7 In the existing reports of organometallics-derived copper catalysts, summarized in Fig. 5c; a more detailed thermodynamic profile metalliccopperhasbeenoftenperceivedastheonlymotifresponsible regarding all reaction intermediates is given in Supplementary forCO reduction42,43.However,inthecurrentcomparativestudyboth Tables6–8.FortheC pathways(blueandblack),the*COcouplingand 2 2 the characterization results and control experiments suggest there subsequentproton-coupledelectrontransfer(PCET)toform*OCCOH exists a synergy between the Cu clusters and partially reduced (2*CO+H++e− → *OCCOH) show the maximum uphill free energy O-containing hexaphyrin complexes in promoting C production, change (ΔG). || The major difference between these two pathways is containingonlyonecoordinatedCuatom.Thisresultsinaconfined whetherCorOon*OCCOHisprotonated.TheprotonationonOto spacebetweentheagglomeratedCuclusterandunreducedsingleCu *HOCCOHisendergonicwithanuphillΔG=0.42eV,incontrasttothe centerinthevicinity.InthefollowingDFTinvestigationsbasedonthis exergonic protonation on C to *OCHCOH (ΔG=–0.09eV), which model(Fig.4f),wewillshowtheresultantuniquecoordinationenvirindicatesthatCO RRcanproceedpreferentiallytowardC HOHfor2 2 5 onment(i.e.,theconfinedspaceaffordinganextraO–Cubond)would mationonR-Hex-2Cu-O/G.Thereasonfortheunfavoredformationof significantlypromoteC–Ccouplingbybreakingthescalingrelation- *HOCCOHliesinthefactthattheprotonationonOisaccompaniedby ship between key intermediates and enhance alcohol selectivity by the cleavage of previously formed O–Cu bond (Supplementary reservingoxygeninthehydroxylgroup44. || (Cu )immobilizedontheCu-reduction-inducedvacancyonHex-2CuOurexperimentsobserveaselectivityincreaseforethylenepro9 O,anddenotedasR-Hex-2Cu-O.ThecurvedstructureofHex-2Cu-O duction starting from –1.3V on Hex-2Cu-O (Supplementary Fig. 7), formsaconfinedspacebetweentheCu clusterandtheadjacentsingle whichisrationalizedbycalculationssuggestingthattheaccelerated 9 Cucenter,whichare~3.84Åapart(SupplementaryFig.34).Thismodel reactionkinetics is led by the decreased activationbarrier with the isreasonableconsideringthesimilarsizeoftheCuclustertothatofthe changeofelectrodepotential.Figure5eshowsthatat0VvsRHEthe hexaphyrinmolecule(Fig.3d).Furthermore,toincludetheimpactof formation of *HOCCOH is kinetically unfavored on R-Hex-2Cu-O/G carbon-basedconductingagentKetjenBlack(KB)intheexperiment,a with an activation energy barrier of 1.51eV (MEP shown in Supple5×5×1 graphene substrate was introduced to support the hybrid mentary Fig. 39).</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>main=P1;P5; mentioned_only=P4; rejected=P1</t>
+          <t>main=P1; mentioned_only=P5</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2149,44 +2077,40 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>P1;P3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>P1;P3</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>isotope;product inference</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Protonation of CH 2 CO* the charge-transfer coefficient of the RDS25,40—we note that the results in surface species CH CO*, OCHCH *, and CH COH*, 3 2 2 RDS approach of determining Tafel slopes is valid only for respectively, all of which tends to be further reduced to C Oxys 2 analyzing the total rate of CO/CO consumption or C /C (Supplementary Figs. 9 and 10).</t>
-        </is>
-      </c>
+          <t>DFT;review</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>main=P1</t>
+          <t>mentioned_only=P1;P3</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2230,33 +2154,17 @@
           <t>ETOH_B2_015_10.1021_acscatal.3c01009.txt</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>DFT;product inference</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>mentioned_only=P5</t>
-        </is>
-      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2266,7 +2174,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2312,14 +2220,10 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
           <t>P1;P2;P3</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
@@ -2328,27 +2232,27 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown</t>
+          <t>DFT;operando/spectroscopy;unknown</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Generally, the enhanced adsorption of PerformanceofCERintheflowcell 2 negativelycharged*COmayfocusontheelectrophilicCusites,while ThecathodicelectrochemicalexperimentsofCO reductionreaction 2 theC endof*C H O,withahighpositivecharge,prefersbondingwith were implemented in flow cells using 1M KOH as electrolyte under 2 2 2 nucleophilicCu O. ambientconditions(SupplementaryFig.19).Allworkingpotentialsare 2 Toanalyzetheoriginsofenhancedrectifyinginterfaces,electro convertedintothereversiblehydrogenelectrode(RHE)scalewithiR paramagnetic resonance (EPR), XPS, and X-ray absorption spectrocorrectionof85%.Thelinearsweepvoltammetry(LSV)curvesinFig.4A scopywereutilizedtocharacterizetherefinedstructureofCu /Cu O. show that the Cu /Cu O catalyst provides higher conductivity and L 2 L 2 AsshowninFig.3A,theO1sXPSspectrumisdeconvolutedintofour activity for CER, with a total current density (j ) of −200 at the total peakssituatedat529.7,530.3,530.8,and531.7eV,correspondingto appliedpotentialof−0.66V.ThesplendidkineticpropertyofCu/Cu O L 2 the lattice oxygen (Cu–O), oxygen vacancies (Vo), C–O bond and revealsasmallercharge-transferresistanceandhighercatalyticactivity adsorbedoxygenonCu /Cu Osamples,respectively38.TheratioofVo/ (tafelslopeof232mVdec−1andelectrochemicallyactivesurfaceareaof L 2 Cu–O demonstrates a descendant trend with Ar+ etching, implying 6.1mFcm−2)forCER(SupplementaryFigs.20and21).Remarkably,Cu / L surfaceandsubsurfaceoxygendeficiencyintheoxide-derivedCu.The Cu O shows excellent selectivity of C alcohols with a maximum 2 2+ shiftofbondingenergyofCu–Otowardahigherlevelalsoindicates faradicefficiency(FE)of64.15±1.92%(ethanolof~56%andn-propanol thedisappearanceofVowithinthedepthofCu /Cu O.Acharacteristic of ~8%), whereas Cu /CuO only reaches a maximum FE and L 2 P 2 ethylene sign of Vo is observed at g=2.004 (Fig. 3B)39, which supports the FE of ~38.4% and 11.4%, respectively (Fig. 4B, C and alcohols NatureCommunications|( 2024)1 5:5172 4</t>
+          <t>In addition, the fren-propanol(Fig.5E,SupplementaryFig.35,andSupplementaryTable6). quenciesofυ(CO)bandsarecorrelatedwiththecoordinationstatesof For the C–C coupling on Cu/CuO model (Fig. 5F, Supplementary L 2 Cusites.Therefore,thelow-coordinationstatesofCusitesinCu /Cu O Fig.36andSupplementaryTable7),the*CO–COHcouplingistherateL 2 willinduceapositiveshiftofthed-bandcenterofCuandboostthe determiningstepforCu/CuOcatalyst(1.46eV),indicatingthevitalrule L 2 hybridizationofthed-bandwiththe2π*orbitalofCO.TheHFBmodes of *CO coverage in the post-coupled proton-electron transfer (CPET) derivedfromthelow-coordinatedCusiteswillfavorthebreedingof reaction.Theenergybarriersofintermediatesgraduallydecreaseuntil theυ(C–C)band(~1960cm−1),whereablueshiftmaypredictthepro- *CHOisreached,whichcanbefurtherreducedto*CH Oor*Ofor 2 3 2 4 tonationprocessC–Cbonds29,30.Onthecontrary,theweaksignsofthe ethanol or CH , respectively. || P 2 L Cu O.IntheRamanspectra(Fig.5BandSupplementaryFig.33D),the Cu/CuOwithadditionallyformedemptyorbitalscanfacilitateelectron 2 L 2 Cu /Cu Opowderloadedoncarbonpapersubstrateexhibitstypical transferfromhydrogentonucleophilicintermediates,suggestingtheCu L 2 characteristic peaks of adsorbed *CO intermediates, which are 3dorbitalsoverlapwiththeπorbitalsofCandfurtherreducedactivation deconvoluted into a low-frequencyband (LFB) at ∼2045cm−1 and a energyforCO hydrogenationonCu/CuO68.Asaresult,thenucleo2 2 high-frequencyband(HFB)at∼2097cm−1,whichverifiesthebonding philic addition reaction process of *CHCO–*CO coupling may effec2 stylesonterraceandstepsites,respectively53,54.Aredshiftoftheυ(CO) tivelyreactonthemixed-valenceboundaryregion33,whichreducesthe bandindicatestheenhancedinteractionbetweenthecatalystsurface formation energy of *CHCOCO on Cu/CuO (−0.148eV) toward 2 L 2 and *CO, resulting in a higher *CO coverage55. || Combining with time-independent spectral analysis (SupoxidationstateofCu+speciesduringCO electroreduction,allowing 2 plementaryFig.33A,B),apparentpeaksaredeterminedat1064and forthesynergisticeffectofCuandCu+species. 1558cm−1, which correspond well to the symmetric and asymmetric ThereactionbarriersforthehydrogenationprocessofC inter2+ vibrationsofthe*OCCOHintermediate,respectively49,50.Inaddition, mediatesonthemodelsofCu/CuOwithandwithoutCl,respectively, 2 thestretchingvibrationat1335and1716cm−1areincloseproximityto werecalculatedbyDFT.Firstly,byanalyzingtheBaderchargeandbond thestretchingof*OCH CH and*CHO,respectively,whichserveasthe length of Cu/CuO (Fig. 5C, D), it is observed that the lower Bader 2 3 L 2 important intermediates for the subsequent C–C coupling in the chargevalue(0.477|e|)comparedtoCu /CuO(1.01|e|)indicatesthat P 2 productionofC alcohols51,52.Theseconclusionsareconsistentwith thepopulatedelectronicorbitalsoflow-coordinatedCusiteswilleasily 2+ theresultsobtainedfromtheproductanalysisofCu /Cu OandCu / bindtointermediatesandreducetherate-determiningenergybarrier67. || Furthermore, Cu /Cu O catalyst L 2 hinder the accumulation of electrons, thereby safeguarding the generatedhighlyselectivecatalyticsitesforthecouplingreactionof integrityofCu–Obonds,whilesimultaneouslyenablingswiftelectron *CO–COHandhydrogenationofC H O*intermediatetoC alcohols. 2 2 2+ transfercourtesyofitsbuilt-inelectricfield12,13.Therefore,itnecessiChlorine-dopedcuprousoxide(Cl–Cu O)andpureCu Owereselec2 2 tatestheemploymentofintricatecatalystconfigurationandfabricated as the precursors and electrochemically reconstructed to tiontechniquestoelevatetherectifyinginterfaceeffectsofCu/Cu O unsaturated-coordinate Cu /Cu O and pure Cu /Cu O. || The low2 L 2 P 2 forthepurposeofbondingoxyhydrocarbons. coordinated Cu /Cu O achieved a C alcohols faradic efficiency L 2 2+ Severalstrategiescanimprovetheselectivityofoxyhydrocarbons (FE )of64.15±1.92%withthecorrespondingenergyefficiencyof alcohols inCER,includingthehighconcentrationoflocal*COaroundtheactive ~39.32%.Inaddition,astableC alcoholsfaradaicefficiencyof&gt;50% 2+ sites14,15,dopingmodificationofcoppercatalystswithheteroatoms16,17, was also obtained during a continuous 50h chronopotentiometry building of crystal defects and low coordination of copper12,18,19. experiment.Ourresearchprovidesaplatformfortherationaldesign Effectively, the coverage of *CO can be facilitated on the lowof low-coordinated Cu–Cu O Mott–Schottky catalysts and analyzes 2 coordinatedCusitesofoxide-derivedCu,leadingtoitssubsequent thekeyelementsforefficientsynthesisofC alcohols. 2+ hydrogenationinto*COH,whichisessentialforthecouplingofOC −COH20,21.Forexample,LianggroupreportedafragmentedCucatalyst Results withabundantlow-coordinatedsitesbyelectrochemicalreconstrucSynthesisandcharacterizationofCu L /Cu 2 Onanoparticles tion ofB-dopedCu O,whichexhibited aC products faradaiceffiThe Cu /Cu O catalysts were synthesized using a simple electro2 2+ L 2 ciencyof77.8%at300mAcm−2(seeref.19).Theoreticalcomputations chemical reconstruction strategy on Cl–Cu O nanoparticles (see 2 havedemonstratedthatthe*CObindingscouldbestrengthenedon detailsin“Methods”,SupplementaryFigs.1–4).TheCu /Cu Ocatalysts L 2 low-coordinated copper sites and prefer to coupling with *COH are designed to function as a Mott–Schottky catalyst of Cu/Cu O, 2 insteadof*COdimerization22.Moreover,theincorporationofhalide which generates enhanced rectifying interfaces between electronspecies and the creation of oxygen vacancy also contribute to the deficientmetalandelectron-richregionbecauseofthedifferencein formationoflow-coordinatedmetalandthecontrolledgenerationof work function (Fig. 1A).</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>main=P2; mentioned_only=P1;P3</t>
+          <t>main=P1;P2;P3</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
